--- a/Finalisasi Skripsi 13-7-2026/4. Analisis Kurikulum/Analisis Kurikulum yang sudah dikonsistenkan.xlsx
+++ b/Finalisasi Skripsi 13-7-2026/4. Analisis Kurikulum/Analisis Kurikulum yang sudah dikonsistenkan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Skripsi\Finalisasi Skripsi 13-7-2026\4. Analisis Kurikulum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{921CFE93-5875-459F-815B-5C1EBD7DD217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D264A4F-0172-41A1-A637-E9FB6F2178BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="0" windowWidth="11520" windowHeight="12960" firstSheet="11" activeTab="12" xr2:uid="{31E38A12-9EAE-43A5-8829-7C49E1584AF9}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12960" firstSheet="11" activeTab="13" xr2:uid="{31E38A12-9EAE-43A5-8829-7C49E1584AF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Agribisnis" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,12 @@
     <sheet name="Sistem Informasi" sheetId="12" r:id="rId11"/>
     <sheet name="Teknik Informatika" sheetId="11" r:id="rId12"/>
     <sheet name="Sheet1" sheetId="13" r:id="rId13"/>
+    <sheet name="Sheet3" sheetId="15" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Agribisnis!$L$24:$N$24</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="858">
   <si>
     <t>Komponen</t>
   </si>
@@ -2603,13 +2603,25 @@
   </si>
   <si>
     <t>S35</t>
+  </si>
+  <si>
+    <t>Inggris</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Ilmu Pengetahuan Sosial</t>
+  </si>
+  <si>
+    <t>Geografi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2654,6 +2666,19 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -2734,7 +2759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2776,6 +2801,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2794,9 +2822,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2814,6 +2839,28 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3201,17 +3248,17 @@
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -3253,10 +3300,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>140</v>
       </c>
@@ -3298,10 +3345,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>144</v>
       </c>
@@ -3343,10 +3390,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>148</v>
       </c>
@@ -3388,10 +3435,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
       <c r="P7" s="6" t="s">
         <v>152</v>
       </c>
@@ -3424,17 +3471,17 @@
       <c r="G8" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="15"/>
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
       <c r="P8" s="6" t="s">
         <v>157</v>
       </c>
@@ -3461,10 +3508,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:20" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
@@ -3477,10 +3524,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -3492,10 +3539,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:20" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -3507,10 +3554,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -3522,23 +3569,23 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="21"/>
+      <c r="J14" s="15"/>
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I15" s="5" t="s">
@@ -3550,10 +3597,10 @@
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I16" s="6" t="s">
@@ -3564,10 +3611,10 @@
       </c>
     </row>
     <row r="17" spans="9:14" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I17" s="21" t="s">
+      <c r="I17" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="15"/>
     </row>
     <row r="18" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I18" s="5" t="s">
@@ -3758,13 +3805,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I8:J8"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="L23:N23"/>
@@ -3781,6 +3821,13 @@
     <mergeCell ref="M13:N13"/>
     <mergeCell ref="M14:N14"/>
     <mergeCell ref="M15:N15"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3857,17 +3904,17 @@
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -3909,10 +3956,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>516</v>
       </c>
@@ -3954,10 +4001,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>519</v>
       </c>
@@ -3999,10 +4046,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>521</v>
       </c>
@@ -4035,10 +4082,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
@@ -4054,10 +4101,10 @@
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
     </row>
     <row r="9" spans="2:20" ht="62.4" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
@@ -4075,10 +4122,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
@@ -4091,10 +4138,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -4106,10 +4153,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -4121,10 +4168,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -4136,10 +4183,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I14" s="6" t="s">
@@ -4151,10 +4198,10 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I15" s="26" t="s">
@@ -4164,10 +4211,10 @@
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I16" s="5" t="s">
@@ -4444,6 +4491,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="I2:J2"/>
@@ -4460,14 +4515,6 @@
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="M12:N12"/>
     <mergeCell ref="M13:N13"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4545,17 +4592,17 @@
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -4597,10 +4644,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>559</v>
       </c>
@@ -4642,10 +4689,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>563</v>
       </c>
@@ -4687,10 +4734,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>567</v>
       </c>
@@ -4732,10 +4779,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
       <c r="P7" s="6" t="s">
         <v>569</v>
       </c>
@@ -4768,17 +4815,17 @@
       <c r="G8" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="15"/>
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
       <c r="P8" s="6" t="s">
         <v>572</v>
       </c>
@@ -4814,10 +4861,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -4835,10 +4882,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -4850,10 +4897,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -4865,10 +4912,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -4880,10 +4927,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="I14" s="6" t="s">
@@ -4895,10 +4942,10 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I15" s="6" t="s">
@@ -4910,16 +4957,16 @@
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I16" s="21" t="s">
+      <c r="I16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="15"/>
     </row>
     <row r="17" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I17" s="5" t="s">
@@ -4962,10 +5009,10 @@
       </c>
     </row>
     <row r="22" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I22" s="21" t="s">
+      <c r="I22" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="21"/>
+      <c r="J22" s="15"/>
     </row>
     <row r="23" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I23" s="5" t="s">
@@ -5180,13 +5227,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="I2:J2"/>
@@ -5203,6 +5243,13 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5282,17 +5329,17 @@
       <c r="G3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="9" t="s">
         <v>12</v>
       </c>
@@ -5337,10 +5384,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>606</v>
       </c>
@@ -5386,10 +5433,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>610</v>
       </c>
@@ -5435,10 +5482,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>613</v>
       </c>
@@ -5483,10 +5530,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
       <c r="P7" s="6" t="s">
         <v>617</v>
       </c>
@@ -5522,17 +5569,17 @@
       <c r="G8" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="15"/>
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
       <c r="P8" s="6" t="s">
         <v>622</v>
       </c>
@@ -5571,10 +5618,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
@@ -5587,10 +5634,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -5602,10 +5649,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -5618,10 +5665,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -5634,10 +5681,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I14" s="6" t="s">
@@ -5649,23 +5696,23 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="15"/>
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="I16" s="5" t="s">
@@ -5712,10 +5759,10 @@
       <c r="N20" s="3"/>
     </row>
     <row r="21" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="21"/>
+      <c r="J21" s="15"/>
       <c r="K21" s="1"/>
       <c r="N21" s="3"/>
     </row>
@@ -5945,16 +5992,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="P2:U2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
     <mergeCell ref="L29:N29"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="L2:N2"/>
@@ -5968,6 +6005,16 @@
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="M15:N15"/>
+    <mergeCell ref="P2:U2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9951,6 +9998,753 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115971E0-C6E1-4825-B102-B8A47D23C65E}">
+  <dimension ref="B2:C106"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5546875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.88671875" style="28" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="29"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="30"/>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B5" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B6" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B7" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B8" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B9" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="29"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="30"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B14" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B15" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B16" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B17" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B18" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B19" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="29"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="34"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B24" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B25" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B26" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B27" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="29"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="30"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B32" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B33" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B34" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B35" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="29" t="s">
+        <v>854</v>
+      </c>
+      <c r="C37" s="29"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="35"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B40" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B41" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B42" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B43" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="29" t="s">
+        <v>855</v>
+      </c>
+      <c r="C45" s="29"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="35"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B48" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B49" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B50" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B51" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="29" t="s">
+        <v>856</v>
+      </c>
+      <c r="C53" s="29"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="30"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B56" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B57" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B58" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B59" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B60" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" s="29"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="30"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B65" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C66" s="32" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B67" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C67" s="32" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B68" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" s="32" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B69" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C69" s="32" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="29" t="s">
+        <v>857</v>
+      </c>
+      <c r="C71" s="29"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C72" s="30"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C74" s="32" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B75" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C75" s="32" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B76" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" s="32" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B77" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C77" s="32" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" s="32" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C80" s="29"/>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C81" s="30"/>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B83" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C83" s="32" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B84" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C84" s="32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B85" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" s="32" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B86" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C86" s="32" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B87" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C87" s="32" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B88" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C88" s="32" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C90" s="29"/>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C91" s="30"/>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B92" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C93" s="32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B94" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C94" s="32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B95" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B96" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C96" s="32" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B97" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C97" s="32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C98" s="32" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B99" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C99" s="32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="29"/>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C102" s="30"/>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B103" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B104" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C104" s="32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B105" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="C105" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B106" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C106" s="32" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10023,17 +10817,17 @@
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -10075,10 +10869,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>195</v>
       </c>
@@ -10120,10 +10914,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>198</v>
       </c>
@@ -10165,10 +10959,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>200</v>
       </c>
@@ -10210,10 +11004,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
       <c r="P7" s="6" t="s">
         <v>203</v>
       </c>
@@ -10255,10 +11049,10 @@
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
       <c r="P8" s="6" t="s">
         <v>207</v>
       </c>
@@ -10291,17 +11085,17 @@
       <c r="G9" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="21"/>
+      <c r="J9" s="15"/>
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
       <c r="P9" s="6" t="s">
         <v>211</v>
       </c>
@@ -10333,10 +11127,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -10358,10 +11152,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -10383,10 +11177,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -10408,10 +11202,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
@@ -10428,10 +11222,10 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I15" s="6" t="s">
@@ -10443,10 +11237,10 @@
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I16" s="6" t="s">
@@ -10482,10 +11276,10 @@
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="I20" s="21" t="s">
+      <c r="I20" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="21"/>
+      <c r="J20" s="15"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="I21" s="5" t="s">
@@ -10544,10 +11338,10 @@
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="I28" s="21" t="s">
+      <c r="I28" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J28" s="21"/>
+      <c r="J28" s="15"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="I29" s="5" t="s">
@@ -10765,13 +11559,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="M4:N4"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="I2:J2"/>
@@ -10788,6 +11575,13 @@
     <mergeCell ref="M8:N8"/>
     <mergeCell ref="M7:N7"/>
     <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10864,17 +11658,17 @@
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -10916,10 +11710,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>247</v>
       </c>
@@ -10961,10 +11755,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>252</v>
       </c>
@@ -11006,10 +11800,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>256</v>
       </c>
@@ -11051,10 +11845,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
       <c r="P7" s="6" t="s">
         <v>261</v>
       </c>
@@ -11087,17 +11881,17 @@
       <c r="G8" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="15"/>
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
       <c r="P8" s="6" t="s">
         <v>266</v>
       </c>
@@ -11133,10 +11927,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -11158,10 +11952,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -11183,10 +11977,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -11208,10 +12002,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -11233,10 +12027,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
@@ -11258,10 +12052,10 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
@@ -11283,10 +12077,10 @@
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
@@ -11299,10 +12093,10 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="I16" s="21" t="s">
+      <c r="I16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="15"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -11390,10 +12184,10 @@
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B22" s="1"/>
-      <c r="I22" s="21" t="s">
+      <c r="I22" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="21"/>
+      <c r="J22" s="15"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -11635,6 +12429,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="L31:N31"/>
     <mergeCell ref="P2:T2"/>
     <mergeCell ref="I3:J3"/>
@@ -11651,13 +12452,6 @@
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11733,17 +12527,17 @@
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -11785,10 +12579,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>295</v>
       </c>
@@ -11830,10 +12624,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>299</v>
       </c>
@@ -11875,10 +12669,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>304</v>
       </c>
@@ -11920,10 +12714,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
       <c r="P7" s="6" t="s">
         <v>309</v>
       </c>
@@ -11956,17 +12750,17 @@
       <c r="G8" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="15"/>
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
       <c r="P8" s="6" t="s">
         <v>313</v>
       </c>
@@ -11999,10 +12793,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
@@ -12015,10 +12809,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -12030,10 +12824,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -12045,10 +12839,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -12060,10 +12854,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I14" s="6" t="s">
@@ -12075,23 +12869,23 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="15"/>
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I16" s="5" t="s">
@@ -12134,10 +12928,10 @@
       </c>
     </row>
     <row r="21" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="21"/>
+      <c r="J21" s="15"/>
     </row>
     <row r="22" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I22" s="5" t="s">
@@ -12339,6 +13133,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="P2:T2"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="E2:G2"/>
@@ -12355,13 +13156,6 @@
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12437,17 +13231,17 @@
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -12489,10 +13283,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>343</v>
       </c>
@@ -12534,10 +13328,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>347</v>
       </c>
@@ -12579,10 +13373,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>350</v>
       </c>
@@ -12624,10 +13418,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
       <c r="P7" s="6" t="s">
         <v>355</v>
       </c>
@@ -12660,17 +13454,17 @@
       <c r="G8" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="15"/>
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
       <c r="P8" s="6" t="s">
         <v>358</v>
       </c>
@@ -12703,10 +13497,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
@@ -12719,10 +13513,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -12734,10 +13528,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -12749,10 +13543,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -12764,10 +13558,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="I14" s="6" t="s">
@@ -12779,23 +13573,23 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="15"/>
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I16" s="5" t="s">
@@ -12838,10 +13632,10 @@
       </c>
     </row>
     <row r="21" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="21"/>
+      <c r="J21" s="15"/>
     </row>
     <row r="22" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I22" s="5" t="s">
@@ -13043,13 +13837,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="I2:J2"/>
@@ -13066,6 +13853,13 @@
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="M12:N12"/>
     <mergeCell ref="M13:N13"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13142,17 +13936,17 @@
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -13194,10 +13988,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>387</v>
       </c>
@@ -13239,10 +14033,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>390</v>
       </c>
@@ -13284,10 +14078,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>394</v>
       </c>
@@ -13329,10 +14123,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
       <c r="P7" s="6" t="s">
         <v>355</v>
       </c>
@@ -13365,17 +14159,17 @@
       <c r="G8" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="15"/>
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
       <c r="P8" s="6" t="s">
         <v>401</v>
       </c>
@@ -13411,10 +14205,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
@@ -13427,10 +14221,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -13442,10 +14236,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:20" ht="46.8" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -13457,10 +14251,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -13472,10 +14266,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I14" s="6" t="s">
@@ -13487,23 +14281,23 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="15"/>
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I16" s="5" t="s">
@@ -13555,10 +14349,10 @@
       </c>
     </row>
     <row r="21" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="21"/>
+      <c r="J21" s="15"/>
       <c r="L21" s="23"/>
       <c r="M21" s="23"/>
       <c r="N21" s="23"/>
@@ -13791,14 +14585,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="M10:N10"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="I2:J2"/>
@@ -13815,6 +14601,14 @@
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="M10:N10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13898,10 +14692,10 @@
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -13943,10 +14737,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>424</v>
       </c>
@@ -13988,10 +14782,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>428</v>
       </c>
@@ -14033,10 +14827,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>431</v>
       </c>
@@ -14069,10 +14863,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
@@ -14088,10 +14882,10 @@
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
     </row>
     <row r="9" spans="2:20" ht="62.4" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
@@ -14109,10 +14903,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
@@ -14125,10 +14919,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -14140,10 +14934,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -14155,10 +14949,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -14170,10 +14964,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:20" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I14" s="6" t="s">
@@ -14185,10 +14979,10 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I15" s="24" t="s">
@@ -14198,10 +14992,10 @@
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I16" s="5" t="s">
@@ -14447,14 +15241,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="M10:N10"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="I2:J2"/>
@@ -14471,6 +15257,14 @@
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="M10:N10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14556,10 +15350,10 @@
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -14604,10 +15398,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>453</v>
       </c>
@@ -14652,10 +15446,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>456</v>
       </c>
@@ -14700,10 +15494,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>458</v>
       </c>
@@ -14739,10 +15533,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
@@ -14758,10 +15552,10 @@
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
     </row>
     <row r="9" spans="2:21" ht="46.8" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
@@ -14779,10 +15573,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
@@ -14795,10 +15589,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -14810,10 +15604,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -14825,10 +15619,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -14840,10 +15634,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="I14" s="6" t="s">
@@ -14855,10 +15649,10 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
       <c r="I15" s="24" t="s">
@@ -14868,10 +15662,10 @@
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.3">
       <c r="I16" s="5" t="s">
@@ -15122,6 +15916,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="P2:U2"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="I2:J2"/>
@@ -15138,14 +15940,6 @@
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="M12:N12"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="P2:U2"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15222,17 +16016,17 @@
       <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="15"/>
       <c r="L3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="16" t="s">
         <v>643</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
       <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
@@ -15274,10 +16068,10 @@
       <c r="L4" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="N4" s="18"/>
+      <c r="N4" s="19"/>
       <c r="P4" s="6" t="s">
         <v>484</v>
       </c>
@@ -15319,10 +16113,10 @@
       <c r="L5" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="N5" s="18"/>
+      <c r="N5" s="19"/>
       <c r="P5" s="6" t="s">
         <v>489</v>
       </c>
@@ -15364,10 +16158,10 @@
       <c r="L6" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="18" t="s">
         <v>631</v>
       </c>
-      <c r="N6" s="18"/>
+      <c r="N6" s="19"/>
       <c r="P6" s="6" t="s">
         <v>494</v>
       </c>
@@ -15403,10 +16197,10 @@
       <c r="L7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="18" t="s">
         <v>637</v>
       </c>
-      <c r="N7" s="18"/>
+      <c r="N7" s="19"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
@@ -15423,17 +16217,17 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="15"/>
       <c r="L8" s="6" t="s">
         <v>633</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="18" t="s">
         <v>644</v>
       </c>
-      <c r="N8" s="18"/>
+      <c r="N8" s="19"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
@@ -15459,10 +16253,10 @@
       <c r="L9" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="18" t="s">
         <v>641</v>
       </c>
-      <c r="N9" s="18"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
@@ -15475,10 +16269,10 @@
       <c r="L10" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="17" t="s">
+      <c r="M10" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="N10" s="18"/>
+      <c r="N10" s="19"/>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I11" s="6" t="s">
@@ -15490,10 +16284,10 @@
       <c r="L11" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="M11" s="18" t="s">
         <v>635</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I12" s="6" t="s">
@@ -15505,10 +16299,10 @@
       <c r="L12" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="N12" s="18"/>
+      <c r="N12" s="19"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I13" s="6" t="s">
@@ -15520,10 +16314,10 @@
       <c r="L13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="N13" s="18"/>
+      <c r="N13" s="19"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I14" s="6" t="s">
@@ -15535,23 +16329,23 @@
       <c r="L14" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="N14" s="19"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="15"/>
       <c r="L15" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="21" t="s">
         <v>647</v>
       </c>
-      <c r="N15" s="20"/>
+      <c r="N15" s="21"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I16" s="5" t="s">
@@ -15594,10 +16388,10 @@
       </c>
     </row>
     <row r="21" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I21" s="21" t="s">
+      <c r="I21" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="21"/>
+      <c r="J21" s="15"/>
     </row>
     <row r="22" spans="9:14" x14ac:dyDescent="0.3">
       <c r="I22" s="5" t="s">
@@ -15805,13 +16599,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="I2:J2"/>
@@ -15828,6 +16615,13 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="M5:N5"/>
     <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
